--- a/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,33; 82,91</t>
+          <t>39,63; 81,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,13; 92,19</t>
+          <t>44,85; 92,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,2; 100,0</t>
+          <t>51,01; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,07; 100,0</t>
+          <t>22,86; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,32; 65,15</t>
+          <t>20,54; 63,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,62; 70,08</t>
+          <t>30,98; 73,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 91,15</t>
+          <t>40,95; 91,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,73; 66,86</t>
+          <t>34,71; 67,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,29; 73,62</t>
+          <t>39,5; 72,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 89,94</t>
+          <t>53,21; 90,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,46; 92,94</t>
+          <t>32,91; 92,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 75,17</t>
+          <t>16,92; 69,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,62; 68,91</t>
+          <t>36,82; 71,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,39; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 100,0</t>
+          <t>17,52; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,46; 91,26</t>
+          <t>57,66; 91,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,9; 78,44</t>
+          <t>44,45; 80,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,59; 93,39</t>
+          <t>51,63; 94,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,1; 100,0</t>
+          <t>23,59; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,95; 80,2</t>
+          <t>47,32; 80,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,75; 70,46</t>
+          <t>44,71; 69,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,09; 96,36</t>
+          <t>70,34; 96,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,59; 93,96</t>
+          <t>39,4; 94,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,42; 88,99</t>
+          <t>26,05; 88,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 70,67</t>
+          <t>14,95; 67,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,98; 100,0</t>
+          <t>52,47; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,15; 87,2</t>
+          <t>23,69; 87,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,45; 91,43</t>
+          <t>41,72; 91,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,21; 66,38</t>
+          <t>29,26; 66,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,73; 100,0</t>
+          <t>58,25; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,28; 100,0</t>
+          <t>47,9; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,8; 83,08</t>
+          <t>43,49; 82,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,29; 58,92</t>
+          <t>29,5; 58,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,41; 96,13</t>
+          <t>65,61; 96,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,17; 90,34</t>
+          <t>52,01; 92,27</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,49; 92,18</t>
+          <t>41,64; 92,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,77; 60,67</t>
+          <t>12,2; 59,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,95; 87,78</t>
+          <t>43,04; 87,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,09; 80,96</t>
+          <t>44,86; 83,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,3; 88,28</t>
+          <t>43,18; 88,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,09; 100,0</t>
+          <t>50,57; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,79; 86,32</t>
+          <t>52,93; 85,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,86; 67,35</t>
+          <t>37,51; 67,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,3; 88,62</t>
+          <t>49,25; 90,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,97; 100,0</t>
+          <t>60,14; 100,0</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,21; 71,98</t>
+          <t>47,98; 73,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,36; 60,95</t>
+          <t>39,11; 61,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,54; 97,15</t>
+          <t>76,05; 97,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,66; 84,29</t>
+          <t>45,78; 84,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>51,93; 74,21</t>
+          <t>52,25; 74,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,34; 66,11</t>
+          <t>47,12; 65,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,69; 84,75</t>
+          <t>61,57; 84,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,43; 93,92</t>
+          <t>61,6; 93,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,35; 70,34</t>
+          <t>52,56; 69,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,56; 60,72</t>
+          <t>46,07; 60,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,61; 86,64</t>
+          <t>71,28; 87,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,36; 85,54</t>
+          <t>62,85; 87,22</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y acudieron a un servicio de urgencias (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7948</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6260</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2437</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5449</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7140</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13396</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14680</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12873</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5108; 10530</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4069; 8369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3569; 6996</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>799; 3497</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2720; 8398</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5071; 11953</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4087; 9129</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>489; 2308</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9069; 17589</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10050; 18382</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9034; 15373</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1910; 5377</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3021</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8955</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3065</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10596</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12261</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4382</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>13617</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23568</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17449</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7447</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1192; 4891</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7891; 15265</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>794; 4532</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>7902; 12499</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8665; 15637</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5721; 10427</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1391; 5899</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9818; 16620</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>18297; 28335</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>14094; 19412</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4109; 9809</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3986</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8483</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7366</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9909</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11734</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10610</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11006</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1650; 5630</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1270; 5760</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2343; 4465</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1551; 5707</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3711; 8171</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5308; 12006</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4597; 7892</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3971; 8289</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6622; 12628</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7860; 15526</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8107; 11884</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7716; 13688</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6808</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2216</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>12607</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8133</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14112</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17192</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10349</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8876</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3764; 8324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1551; 7599</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2954</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4599; 9377</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8689; 16237</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5081; 10400</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3812; 7538</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10440; 16855</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>12034; 21788</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7251; 13256</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>6083; 10115</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>21408</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25402</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11718</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>19726</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>51034</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>67174</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>51282</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>16940; 26030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20223; 31799</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>17772; 22752</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7852; 14574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>24310; 34737</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34579; 48331</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25073; 34505</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14805; 22556</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>43009; 57257</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>57634; 76231</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>45684; 56366</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>25883; 35922</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 81,7</t>
+          <t>39,41; 82,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,85; 92,24</t>
+          <t>38,28; 92,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,01; 100,0</t>
+          <t>49,48; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,86; 100,0</t>
+          <t>25,34; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,54; 63,42</t>
+          <t>20,41; 64,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,98; 73,02</t>
+          <t>31,56; 73,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 91,47</t>
+          <t>44,78; 91,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,18; 100,0</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>34,71; 67,31</t>
+          <t>35,98; 67,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,5; 72,25</t>
+          <t>39,41; 74,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,21; 90,56</t>
+          <t>53,31; 90,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,91; 92,63</t>
+          <t>33,12; 93,06</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,92; 69,43</t>
+          <t>17,1; 70,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 71,23</t>
+          <t>36,27; 69,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,52; 100,0</t>
+          <t>17,39; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,66; 91,21</t>
+          <t>54,46; 91,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,45; 80,21</t>
+          <t>42,83; 79,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,63; 94,09</t>
+          <t>48,17; 89,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,59; 100,0</t>
+          <t>21,46; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,32; 80,1</t>
+          <t>47,4; 80,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,71; 69,23</t>
+          <t>44,77; 68,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,34; 96,88</t>
+          <t>70,38; 96,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 94,03</t>
+          <t>38,09; 94,0</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 88,92</t>
+          <t>27,6; 89,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 67,78</t>
+          <t>14,48; 67,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,47; 100,0</t>
+          <t>54,14; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,69; 87,19</t>
+          <t>21,9; 88,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,72; 91,87</t>
+          <t>38,36; 91,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,26; 66,18</t>
+          <t>27,91; 64,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,25; 100,0</t>
+          <t>57,32; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,9; 100,0</t>
+          <t>56,34; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,49; 82,93</t>
+          <t>44,95; 83,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,5; 58,28</t>
+          <t>30,32; 59,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65,61; 96,18</t>
+          <t>66,81; 96,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,01; 92,27</t>
+          <t>46,68; 90,36</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>41,64; 92,09</t>
+          <t>48,89; 92,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 59,79</t>
+          <t>12,31; 60,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1157,42 +1157,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,04; 87,76</t>
+          <t>44,34; 88,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,86; 83,82</t>
+          <t>41,63; 81,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,18; 88,37</t>
+          <t>47,92; 88,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,57; 100,0</t>
+          <t>51,47; 100,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,93; 85,45</t>
+          <t>52,26; 85,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 67,92</t>
+          <t>39,1; 68,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,25; 90,03</t>
+          <t>45,73; 85,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>60,14; 100,0</t>
+          <t>64,48; 100,0</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>47,98; 73,73</t>
+          <t>46,15; 72,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,11; 61,49</t>
+          <t>36,98; 60,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,05; 97,36</t>
+          <t>73,31; 96,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,78; 84,98</t>
+          <t>47,07; 85,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,25; 74,66</t>
+          <t>52,74; 74,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,12; 65,87</t>
+          <t>47,51; 66,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,57; 84,73</t>
+          <t>61,89; 84,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,6; 93,85</t>
+          <t>63,09; 93,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,56; 69,97</t>
+          <t>53,37; 70,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,07; 60,94</t>
+          <t>46,54; 60,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71,28; 87,94</t>
+          <t>70,74; 87,58</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,22</t>
+          <t>62,85; 87,16</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5108; 10530</t>
+          <t>5079; 10678</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4069; 8369</t>
+          <t>3473; 8353</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3569; 6996</t>
+          <t>3461; 6996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>799; 3497</t>
+          <t>886; 3497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2720; 8398</t>
+          <t>2703; 8507</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5071; 11953</t>
+          <t>5167; 12039</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4087; 9129</t>
+          <t>4470; 9139</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>489; 2308</t>
+          <t>0; 2308</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9069; 17589</t>
+          <t>9401; 17550</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10050; 18382</t>
+          <t>10027; 18910</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9034; 15373</t>
+          <t>9049; 15347</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1910; 5377</t>
+          <t>1923; 5402</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1192; 4891</t>
+          <t>1205; 4955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7891; 15265</t>
+          <t>7773; 14853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>794; 4532</t>
+          <t>788; 4532</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7902; 12499</t>
+          <t>7463; 12501</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8665; 15637</t>
+          <t>8349; 15439</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5721; 10427</t>
+          <t>5338; 9873</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1391; 5899</t>
+          <t>1266; 5899</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9818; 16620</t>
+          <t>9834; 16728</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18297; 28335</t>
+          <t>18324; 28204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14094; 19412</t>
+          <t>14101; 19396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4109; 9809</t>
+          <t>3973; 9805</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1650; 5630</t>
+          <t>1748; 5644</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1270; 5760</t>
+          <t>1230; 5699</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2343; 4465</t>
+          <t>2417; 4465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1551; 5707</t>
+          <t>1433; 5766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3711; 8171</t>
+          <t>3412; 8177</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5308; 12006</t>
+          <t>5064; 11631</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4597; 7892</t>
+          <t>4524; 7892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3971; 8289</t>
+          <t>4670; 8289</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6622; 12628</t>
+          <t>6845; 12662</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7860; 15526</t>
+          <t>8077; 15878</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8107; 11884</t>
+          <t>8255; 11893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7716; 13688</t>
+          <t>6924; 13405</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3764; 8324</t>
+          <t>4419; 8338</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1551; 7599</t>
+          <t>1565; 7630</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2289,42 +2289,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4599; 9377</t>
+          <t>4738; 9490</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8689; 16237</t>
+          <t>8064; 15774</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5081; 10400</t>
+          <t>5639; 10424</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3812; 7538</t>
+          <t>3880; 7538</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10440; 16855</t>
+          <t>10307; 16871</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12034; 21788</t>
+          <t>12542; 21879</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7251; 13256</t>
+          <t>6733; 12628</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6083; 10115</t>
+          <t>6522; 10115</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16940; 26030</t>
+          <t>16294; 25613</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20223; 31799</t>
+          <t>19123; 31080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17772; 22752</t>
+          <t>17133; 22651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7852; 14574</t>
+          <t>8073; 14610</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24310; 34737</t>
+          <t>24536; 34588</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34579; 48331</t>
+          <t>34859; 48560</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25073; 34505</t>
+          <t>25204; 34525</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14805; 22556</t>
+          <t>15164; 22468</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43009; 57257</t>
+          <t>43669; 57426</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57634; 76231</t>
+          <t>58216; 76037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45684; 56366</t>
+          <t>45339; 56135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25883; 35922</t>
+          <t>25886; 35896</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$urgencias-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>41,14%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51,44%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71,54%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>61,67%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>68,99%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>81,97%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,54%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,41; 82,85</t>
+          <t>24,32; 65,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,28; 92,07</t>
+          <t>29,62; 70,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,48; 100,0</t>
+          <t>37,92; 91,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,34; 100,0</t>
+          <t>21,14; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 64,24</t>
+          <t>38,33; 82,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 73,54</t>
+          <t>38,13; 92,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,78; 91,57</t>
+          <t>42,2; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>9,57; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,98; 67,16</t>
+          <t>35,73; 66,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,41; 74,32</t>
+          <t>40,29; 73,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53,31; 90,41</t>
+          <t>52,27; 89,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,12; 93,06</t>
+          <t>31,73; 94,65</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>42,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>52,76%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>77,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>62,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>76,65%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,1; 70,33</t>
+          <t>54,46; 91,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,27; 69,3</t>
+          <t>41,9; 78,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>51,59; 93,39</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12,95; 100,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,06; 75,17</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,62; 68,91</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17,39; 100,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>54,46; 91,23</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>42,83; 79,2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>48,17; 89,09</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 100,0</t>
+          <t>17,38; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,4; 80,63</t>
+          <t>46,95; 80,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,77; 68,91</t>
+          <t>44,75; 70,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,38; 96,8</t>
+          <t>71,09; 96,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,09; 94,0</t>
+          <t>36,94; 93,96</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>57,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>38,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>89,27%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>55,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>73,22%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,6; 89,13</t>
+          <t>39,45; 91,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 67,06</t>
+          <t>29,21; 66,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,14; 100,0</t>
+          <t>50,73; 100,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21,9; 88,08</t>
+          <t>48,37; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,36; 91,92</t>
+          <t>26,42; 88,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,91; 64,12</t>
+          <t>15,32; 70,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,32; 100,0</t>
+          <t>51,98; 100,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,34; 100,0</t>
+          <t>21,73; 87,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44,95; 83,16</t>
+          <t>44,8; 83,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,32; 59,6</t>
+          <t>29,29; 58,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,81; 96,25</t>
+          <t>66,41; 96,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,68; 90,36</t>
+          <t>49,16; 89,81</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,36%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>65,08%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83,71%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>75,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36,08%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>75,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>71,55%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,89; 92,25</t>
+          <t>41,95; 87,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 60,03</t>
+          <t>43,09; 80,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>43,3; 88,28</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53,06; 100,0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,49; 92,18</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17,77; 60,67</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>44,34; 88,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,63; 81,43</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,92; 88,57</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51,47; 100,0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52,26; 85,53</t>
+          <t>52,79; 86,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,1; 68,2</t>
+          <t>36,86; 67,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,73; 85,77</t>
+          <t>45,3; 88,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64,48; 100,0</t>
+          <t>63,14; 100,0</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56,93%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74,63%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>81,09%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>60,64%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>49,12%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>89,39%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,15; 72,55</t>
+          <t>51,93; 74,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,98; 60,1</t>
+          <t>46,34; 66,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,31; 96,93</t>
+          <t>61,69; 84,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47,07; 85,19</t>
+          <t>60,56; 93,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,74; 74,34</t>
+          <t>47,21; 71,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,51; 66,18</t>
+          <t>38,36; 60,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,89; 84,78</t>
+          <t>74,54; 97,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,09; 93,49</t>
+          <t>48,84; 85,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53,37; 70,18</t>
+          <t>53,35; 70,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,54; 60,79</t>
+          <t>45,56; 60,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70,74; 87,58</t>
+          <t>69,61; 86,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,85; 87,16</t>
+          <t>61,46; 85,56</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5449</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7140</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>7948</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>6260</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5734</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8420</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7140</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4167</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5079; 10678</t>
+          <t>3221; 8627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3473; 8353</t>
+          <t>4849; 11471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3461; 6996</t>
+          <t>3785; 9098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>886; 3497</t>
+          <t>468; 2213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2703; 8507</t>
+          <t>4939; 10686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5167; 12039</t>
+          <t>3460; 8364</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4470; 9139</t>
+          <t>2952; 6996</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2308</t>
+          <t>349; 3644</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9401; 17550</t>
+          <t>9336; 17469</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10027; 18910</t>
+          <t>10252; 18732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9049; 15347</t>
+          <t>8874; 15268</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1923; 5402</t>
+          <t>1858; 5544</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10596</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8494</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3021</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11306</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10596</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12261</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8494</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7432</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1205; 4955</t>
+          <t>7462; 12505</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7773; 14853</t>
+          <t>8169; 15292</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>5717; 10350</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>751; 5795</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1202; 5296</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7635; 14768</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>788; 4532</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7463; 12501</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8349; 15439</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5338; 9873</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1266; 5899</t>
+          <t>802; 4615</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9834; 16728</t>
+          <t>9742; 16640</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18324; 28204</t>
+          <t>18315; 28838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14101; 19396</t>
+          <t>14245; 19308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3973; 9805</t>
+          <t>3845; 9782</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8483</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6541</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3250</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3986</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6277</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8483</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6625</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10141</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1748; 5644</t>
+          <t>3509; 8132</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1230; 5699</t>
+          <t>5299; 12042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2417; 4465</t>
+          <t>4004; 7892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1433; 5766</t>
+          <t>3626; 7498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3412; 8177</t>
+          <t>1673; 5635</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5064; 11631</t>
+          <t>1302; 6006</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4524; 7892</t>
+          <t>2321; 4465</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4670; 8289</t>
+          <t>1381; 5577</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6845; 12662</t>
+          <t>6822; 12650</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8077; 15878</t>
+          <t>7803; 15695</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8255; 11893</t>
+          <t>8206; 11878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6924; 13405</t>
+          <t>6809; 12438</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8133</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5647</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6808</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4585</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2216</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7304</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12607</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8133</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8876</t>
+          <t>8219</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4419; 8338</t>
+          <t>4482; 9379</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1565; 7630</t>
+          <t>8347; 15683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>5096; 10389</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3579; 6746</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3841; 8332</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2259; 7711</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0; 2954</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>4738; 9490</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8064; 15774</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>5639; 10424</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3880; 7538</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10307; 16871</t>
+          <t>10412; 17026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12542; 21879</t>
+          <t>11826; 21606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6733; 12628</t>
+          <t>6669; 13047</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6522; 10115</t>
+          <t>5883; 9318</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>29626</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41772</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30392</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>21408</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>25402</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>20890</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>11718</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>29626</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>41772</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>30392</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29960</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16294; 25613</t>
+          <t>24159; 34526</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19123; 31080</t>
+          <t>34003; 48513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17133; 22651</t>
+          <t>25123; 34515</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8073; 14610</t>
+          <t>13475; 20795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24536; 34588</t>
+          <t>16668; 25410</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34859; 48560</t>
+          <t>19839; 31517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25204; 34525</t>
+          <t>17420; 22702</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15164; 22468</t>
+          <t>8392; 14651</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>43669; 57426</t>
+          <t>43659; 57555</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58216; 76037</t>
+          <t>56997; 75948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45339; 56135</t>
+          <t>44615; 55531</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25886; 35896</t>
+          <t>24237; 33742</t>
         </is>
       </c>
     </row>
